--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487763_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487763_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7579</v>
+        <v>7.1358</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6527</v>
+        <v>5.8251</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1053</v>
+        <v>1.3108</v>
       </c>
       <c r="G2" t="n">
         <v>2.5156</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0967</v>
+        <v>1.4746</v>
       </c>
       <c r="T2" t="n">
-        <v>1.034</v>
+        <v>1.2064</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.2682</v>
       </c>
       <c r="V2" t="n">
         <v>2.1051</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9364</v>
+        <v>5.0022</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6728</v>
+        <v>3.5912</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2637</v>
+        <v>1.411</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5277</v>
+        <v>1.7204</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3644</v>
+        <v>0.2108</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1633</v>
+        <v>1.5096</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0056</v>
+        <v>2.1818</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8096</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1959</v>
+        <v>1.2932</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4779</v>
+        <v>-0.4614</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4452</v>
+        <v>-0.6778</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0326</v>
+        <v>0.2164</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.0406</v>
+        <v>0.2081</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.1218</v>
+        <v>-1.2487</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0812</v>
+        <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3255</v>
+        <v>1.3224</v>
       </c>
       <c r="T3" t="n">
-        <v>2.789</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5365</v>
+        <v>0.4156</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1238</v>
+        <v>1.7513</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>G. CLARKE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7902</v>
+        <v>4.7442</v>
       </c>
       <c r="E4" t="n">
-        <v>3.526</v>
+        <v>1.8913</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2642</v>
+        <v>2.8529</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7204</v>
+        <v>1.5054</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2108</v>
+        <v>3.0999</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5096</v>
+        <v>-1.5945</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1818</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8885999999999999</v>
+        <v>3.1572</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2932</v>
+        <v>-2.2395</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4614</v>
+        <v>0.5877</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6778</v>
+        <v>-0.0573</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2164</v>
+        <v>0.645</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2081</v>
+        <v>2.4974</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4568</v>
+        <v>2.4974</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1104</v>
+        <v>1.2012</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8416</v>
+        <v>0.9735</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2688</v>
+        <v>0.2277</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7513</v>
+        <v>-0.4599</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. CLARKE</t>
+          <t>M. BILALOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.6252</v>
+        <v>4.2109</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2127</v>
+        <v>1.1717</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4125</v>
+        <v>3.0393</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5054</v>
+        <v>-0.3874</v>
       </c>
       <c r="H5" t="n">
-        <v>3.0999</v>
+        <v>-1.1067</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5945</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9177999999999999</v>
+        <v>-0.5097</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1572</v>
+        <v>-0.335</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.2395</v>
+        <v>-0.1747</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5877</v>
+        <v>0.1223</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0573</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.645</v>
+        <v>0.894</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4974</v>
+        <v>2.2893</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4974</v>
+        <v>2.2893</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0823</v>
+        <v>1.1416</v>
       </c>
       <c r="T5" t="n">
-        <v>1.295</v>
+        <v>0.5139</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2127</v>
+        <v>0.6277</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4599</v>
+        <v>1.1675</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BILALOVIC</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.3592</v>
+        <v>2.7023</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8502</v>
+        <v>0.1726</v>
       </c>
       <c r="F6" t="n">
-        <v>3.509</v>
+        <v>2.5297</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3874</v>
+        <v>1.5277</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1067</v>
+        <v>1.3644</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.1633</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5097</v>
+        <v>2.0056</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.335</v>
+        <v>1.8096</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1747</v>
+        <v>0.1959</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1223</v>
+        <v>-0.4779</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.4452</v>
       </c>
       <c r="O6" t="n">
-        <v>0.894</v>
+        <v>-0.0326</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2893</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2893</v>
+        <v>2.0812</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2898</v>
+        <v>2.0913</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1924</v>
+        <v>1.2888</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0974</v>
+        <v>0.8025</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1675</v>
+        <v>0.1238</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0893</v>
+        <v>1.4951</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6633</v>
+        <v>1.1571</v>
       </c>
       <c r="F7" t="n">
-        <v>0.426</v>
+        <v>0.3379</v>
       </c>
       <c r="G7" t="n">
         <v>1.4214</v>
@@ -1000,13 +1000,13 @@
         <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5402</v>
+        <v>-0.1344</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.047</v>
+        <v>-0.0411</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>S. CECILIA PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1563</v>
+        <v>-0.0164</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4975</v>
+        <v>-1.6993</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3412</v>
+        <v>1.6829</v>
       </c>
       <c r="G8" t="n">
-        <v>0.38</v>
+        <v>-2.0766</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3711</v>
+        <v>-1.3989</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.6776</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7883</v>
+        <v>-1.7947</v>
       </c>
       <c r="K8" t="n">
-        <v>0.71</v>
+        <v>-1.1497</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0784</v>
+        <v>-0.645</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4083</v>
+        <v>-0.2818</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3389</v>
+        <v>-0.2492</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0694</v>
+        <v>-0.0326</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2893</v>
+        <v>-2.0812</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6649</v>
+        <v>2.0812</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0256</v>
+        <v>0.5389</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7111</v>
+        <v>0.4253</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3145</v>
+        <v>0.1136</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9376</v>
+        <v>1.5213</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7076</v>
+        <v>1.7513</v>
       </c>
       <c r="X8" t="n">
         <v>-0.23</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. CECILIA PEREZ</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6211</v>
+        <v>-0.4979</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1279</v>
+        <v>-0.8353</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5068</v>
+        <v>0.3374</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0766</v>
+        <v>0.8063</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3989</v>
+        <v>1.226</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6776</v>
+        <v>-0.4196</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7947</v>
+        <v>1.1249</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1497</v>
+        <v>1.7609</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.645</v>
+        <v>-0.636</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2818</v>
+        <v>-0.3186</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2492</v>
+        <v>-0.5349</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0326</v>
+        <v>0.2164</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0812</v>
+        <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0659</v>
+        <v>0.2796</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0033</v>
+        <v>0.121</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0626</v>
+        <v>0.1586</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5213</v>
+        <v>-1.1675</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2582</v>
+        <v>-0.6959</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4782</v>
+        <v>-1.8609</v>
       </c>
       <c r="F10" t="n">
-        <v>0.22</v>
+        <v>1.165</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8063</v>
+        <v>0.38</v>
       </c>
       <c r="H10" t="n">
-        <v>1.226</v>
+        <v>0.3711</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4196</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1249</v>
+        <v>0.7883</v>
       </c>
       <c r="K10" t="n">
-        <v>1.7609</v>
+        <v>0.71</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.636</v>
+        <v>0.0784</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3186</v>
+        <v>-0.4083</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5349</v>
+        <v>-0.3389</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2164</v>
+        <v>-0.0694</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4162</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0812</v>
+        <v>-2.2893</v>
       </c>
       <c r="R10" t="n">
         <v>1.6649</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4808</v>
+        <v>0.486</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5219</v>
+        <v>0.3477</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0411</v>
+        <v>0.1383</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1675</v>
+        <v>-0.9376</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6717</v>
+        <v>-1.3987</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8937</v>
+        <v>-0.6794</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.778</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0.3385</v>
@@ -1312,13 +1312,13 @@
         <v>0.4162</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9492</v>
+        <v>1.2223</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.733</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4306</v>
+        <v>0.4893</v>
       </c>
       <c r="V11" t="n">
         <v>-2.3351</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4243</v>
+        <v>-5.9289</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.3446</v>
+        <v>-6.1722</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0796</v>
+        <v>0.2433</v>
       </c>
       <c r="G12" t="n">
         <v>-7.3223</v>
@@ -1390,13 +1390,13 @@
         <v>1.8731</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1468</v>
+        <v>0.6421</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5153</v>
+        <v>0.6877</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3686</v>
+        <v>-0.0456</v>
       </c>
       <c r="V12" t="n">
         <v>1.1675</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.4266</v>
+        <v>16.7527</v>
       </c>
       <c r="E13" t="n">
-        <v>2.235799999999999</v>
+        <v>2.5619</v>
       </c>
       <c r="F13" t="n">
-        <v>14.1911</v>
+        <v>14.1909</v>
       </c>
       <c r="G13" t="n">
         <v>0.4289999999999994</v>
@@ -1450,10 +1450,10 @@
         <v>0.6733999999999996</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.2065</v>
+        <v>-4.206500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.8394</v>
+        <v>-5.839399999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1.6332</v>
@@ -1468,16 +1468,16 @@
         <v>19.7711</v>
       </c>
       <c r="S13" t="n">
-        <v>9.939400000000001</v>
+        <v>10.2656</v>
       </c>
       <c r="T13" t="n">
-        <v>6.7846</v>
+        <v>7.110799999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>3.1547</v>
+        <v>3.1548</v>
       </c>
       <c r="V13" t="n">
-        <v>2.936400000000001</v>
+        <v>2.9364</v>
       </c>
       <c r="W13" t="n">
         <v>7.4651</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MENENDEZ GARCIA</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1515</v>
+        <v>0.444</v>
       </c>
       <c r="E14" t="n">
-        <v>0.767</v>
+        <v>-1.181</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3845</v>
+        <v>1.625</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9536</v>
+        <v>0.3077</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4564</v>
+        <v>0.013</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4972</v>
+        <v>0.2947</v>
       </c>
       <c r="J14" t="n">
-        <v>3.901</v>
+        <v>-0.5209</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1956</v>
+        <v>-0.5992</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7054</v>
+        <v>0.0784</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9474</v>
+        <v>0.8286</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7393</v>
+        <v>0.6122</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2082</v>
+        <v>0.2164</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4162</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.3299</v>
+        <v>-1.0406</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9137</v>
+        <v>0.8325</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4893</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9035</v>
+        <v>0.1505</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4142</v>
+        <v>-0.7437</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.8751</v>
+        <v>0.9376</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.7076</v>
+        <v>0.23</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.1675</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>G. ARCOS GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7272999999999999</v>
+        <v>-0.0757</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0738</v>
+        <v>-1.9467</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8011</v>
+        <v>1.871</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3077</v>
+        <v>0.0286</v>
       </c>
       <c r="H15" t="n">
-        <v>0.013</v>
+        <v>0.6695</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2947</v>
+        <v>-0.6409</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5209</v>
+        <v>-0.163</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5992</v>
+        <v>0.0207</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0784</v>
+        <v>-0.1837</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8286</v>
+        <v>0.1916</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6122</v>
+        <v>0.6488</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2164</v>
+        <v>-0.4572</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0406</v>
+        <v>-2.2893</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8325</v>
+        <v>2.7055</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3099</v>
+        <v>-1.6881</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2577</v>
+        <v>-0.6619</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5675</v>
+        <v>-1.0261</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9376</v>
+        <v>1.1675</v>
       </c>
       <c r="W15" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. ARCOS GONZALEZ</t>
+          <t>J. MENENDEZ GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5425</v>
+        <v>-0.3604</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.5896</v>
+        <v>-0.3046</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0471</v>
+        <v>-0.0559</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0286</v>
+        <v>2.9536</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6695</v>
+        <v>2.4564</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6409</v>
+        <v>0.4972</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.163</v>
+        <v>3.901</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0207</v>
+        <v>3.1956</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1837</v>
+        <v>0.7054</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1916</v>
+        <v>-0.9474</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6488</v>
+        <v>-0.7393</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4572</v>
+        <v>-0.2082</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4162</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2893</v>
+        <v>-3.3299</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7055</v>
+        <v>2.9137</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.1548</v>
+        <v>-1.0226</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3049</v>
+        <v>-0.1681</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.85</v>
+        <v>-0.8546</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1675</v>
+        <v>-1.8751</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1675</v>
+        <v>-0.7076</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7476</v>
+        <v>-0.523</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8134</v>
+        <v>-0.7062</v>
       </c>
       <c r="F17" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.1832</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8259</v>
@@ -1780,13 +1780,13 @@
         <v>0.4162</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3379</v>
+        <v>-0.1134</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1422</v>
+        <v>-0.0248</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. BARROS GARCIA</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1326</v>
+        <v>-1.0998</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0866</v>
+        <v>0.8252</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.046</v>
+        <v>-1.925</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3197</v>
+        <v>1.0749</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6055</v>
+        <v>1.128</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2857</v>
+        <v>-0.0531</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0192</v>
+        <v>2.4101</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0192</v>
+        <v>2.0059</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.4041</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3389</v>
+        <v>-1.3352</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6247</v>
+        <v>-0.878</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2857</v>
+        <v>-0.4572</v>
       </c>
       <c r="P18" t="n">
         <v>-0.6244</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>-3.3299</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4162</v>
+        <v>2.7055</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1885</v>
+        <v>-1.4265</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.4662</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1233</v>
+        <v>-0.9603</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.1238</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.2112</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>S. BARROS GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2418</v>
+        <v>-1.1033</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1822</v>
+        <v>-1.0866</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4241</v>
+        <v>-0.0166</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0749</v>
+        <v>-0.3197</v>
       </c>
       <c r="H19" t="n">
-        <v>1.128</v>
+        <v>-0.6055</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0531</v>
+        <v>0.2857</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4101</v>
+        <v>0.0192</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0059</v>
+        <v>0.0192</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4041</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3352</v>
+        <v>-0.3389</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.878</v>
+        <v>-0.6247</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4572</v>
+        <v>0.2857</v>
       </c>
       <c r="P19" t="n">
         <v>-0.6244</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.3299</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7055</v>
+        <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.5685</v>
+        <v>-0.1592</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1091</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.4594</v>
+        <v>-0.0939</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1238</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2112</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3351</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7618</v>
+        <v>-1.7372</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5331</v>
+        <v>-1.8902</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2287</v>
+        <v>0.153</v>
       </c>
       <c r="G20" t="n">
         <v>1.7052</v>
@@ -2014,13 +2014,13 @@
         <v>2.2893</v>
       </c>
       <c r="S20" t="n">
-        <v>-3.4264</v>
+        <v>-2.4018</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4354</v>
+        <v>-0.7924</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.9911</v>
+        <v>-1.6094</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. LUIS</t>
+          <t>S. FRANCO GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0758</v>
+        <v>-3.6565</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9423</v>
+        <v>-2.1125</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1335</v>
+        <v>-1.5441</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2558</v>
+        <v>-2.7883</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.5694</v>
+        <v>-1.2535</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3136</v>
+        <v>-1.5349</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.386</v>
+        <v>-1.7594</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5527</v>
+        <v>0.3838</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1667</v>
+        <v>-2.1431</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8697</v>
+        <v>-1.029</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0167</v>
+        <v>-1.6372</v>
       </c>
       <c r="O21" t="n">
-        <v>0.147</v>
+        <v>0.6082</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
         <v>1.4568</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9094</v>
+        <v>-1.2844</v>
       </c>
       <c r="T21" t="n">
-        <v>1.295</v>
+        <v>-0.48</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3855</v>
+        <v>-0.8044</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1051</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3351</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. FRANCO GARCIA</t>
+          <t>M. OKAFOR AUGUSTIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8811</v>
+        <v>-3.9428</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2196</v>
+        <v>-3.6675</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6615</v>
+        <v>-0.2753</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7883</v>
+        <v>-1.3093</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2535</v>
+        <v>0.7146</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5349</v>
+        <v>-2.0239</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7594</v>
+        <v>-0.909</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3838</v>
+        <v>0.4413</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.1431</v>
+        <v>-1.3504</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.029</v>
+        <v>-0.4002</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6372</v>
+        <v>0.2733</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6082</v>
+        <v>-0.6735</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4162</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0406</v>
+        <v>-2.2893</v>
       </c>
       <c r="R22" t="n">
         <v>1.4568</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.509</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9218</v>
+        <v>-0.1643</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.9376</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X22" t="n">
         <v>-1.1675</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. OKAFOR AUGUSTIN</t>
+          <t>J. LUIS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9222</v>
+        <v>-4.3719</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8818</v>
+        <v>-2.121</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0404</v>
+        <v>-2.2509</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3093</v>
+        <v>-1.2558</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7146</v>
+        <v>-2.5694</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0239</v>
+        <v>1.3136</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.909</v>
+        <v>-0.386</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4413</v>
+        <v>-1.5527</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3504</v>
+        <v>1.1667</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4002</v>
+        <v>-0.8697</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2733</v>
+        <v>-1.0167</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6735</v>
+        <v>0.147</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.8325</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2893</v>
+        <v>-2.0812</v>
       </c>
       <c r="R23" t="n">
         <v>1.4568</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8429</v>
+        <v>-0.3867</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9134</v>
+        <v>0.1162</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07049999999999999</v>
+        <v>-0.503</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9376</v>
+        <v>-2.1051</v>
       </c>
       <c r="W23" t="n">
         <v>0.23</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1675</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="24">
@@ -2284,13 +2284,13 @@
         <v>-16.4266</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.191</v>
+        <v>-14.1911</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2358</v>
+        <v>-2.2356</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4289999999999998</v>
+        <v>-0.429</v>
       </c>
       <c r="H24" t="n">
         <v>1.8774</v>
@@ -2299,10 +2299,10 @@
         <v>-2.3066</v>
       </c>
       <c r="J24" t="n">
-        <v>4.206499999999998</v>
+        <v>4.2065</v>
       </c>
       <c r="K24" t="n">
-        <v>5.8394</v>
+        <v>5.839399999999999</v>
       </c>
       <c r="L24" t="n">
         <v>-1.6329</v>
@@ -2326,16 +2326,16 @@
         <v>16.6493</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.9392</v>
+        <v>-9.939299999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.1547</v>
+        <v>-3.1548</v>
       </c>
       <c r="U24" t="n">
         <v>-6.7845</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.936500000000001</v>
+        <v>-2.9365</v>
       </c>
       <c r="W24" t="n">
         <v>4.528600000000001</v>
